--- a/Task1/Инициативы.xlsx
+++ b/Task1/Инициативы.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sergej/Documents/GitHub/Solution-AI-Sprint7/Task1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DCB16F7A-5C49-424B-BF87-CE35CD0120DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A5EB33-A9F5-4540-9A2F-49945FCD7C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39600" yWindow="6220" windowWidth="28240" windowHeight="17240" xr2:uid="{D60D4A63-72E7-4F4F-A707-7ECDF5E29F8D}"/>
+    <workbookView xWindow="4160" yWindow="2680" windowWidth="28240" windowHeight="17240" xr2:uid="{D60D4A63-72E7-4F4F-A707-7ECDF5E29F8D}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -191,15 +191,9 @@
     <t>1. Автоматически выявлять подозрительные операции по счетам (транзит, обналичивание, дробление платежей под пороги).</t>
   </si>
   <si>
-    <t>Проводить анализ операция по счетам и присваивать признак  "Подозрительная операция"</t>
-  </si>
-  <si>
     <t>Выход модели против бизнес выхода</t>
   </si>
   <si>
-    <t xml:space="preserve">На выходе отсеиваем от обычных операций подозрительные </t>
-  </si>
-  <si>
     <t xml:space="preserve">Выявленая подозрительная операция (либо по определенному алгоритму, либо с помощью ML - зависит от ответов от бизнеса) </t>
   </si>
   <si>
@@ -225,6 +219,12 @@
   </si>
   <si>
     <t>История проверок ушедших клиентов и определние закономерностей ухода клиента</t>
+  </si>
+  <si>
+    <t>Проводить анализ операций по счетам и присваивать признак  "Подозрительная операция"</t>
+  </si>
+  <si>
+    <t>На выходе помечаются в автоматическом режиме операции с признаком подозрительные - для приоритизации разбора таких операций сотрудниками</t>
   </si>
 </sst>
 </file>
@@ -290,11 +290,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -807,7 +807,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -906,67 +906,67 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
     </row>
     <row r="23" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="51" x14ac:dyDescent="0.2">
-      <c r="A24" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D24" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="51" x14ac:dyDescent="0.2">
-      <c r="A25" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A26" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/Task1/Инициативы.xlsx
+++ b/Task1/Инициативы.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sergej/Documents/GitHub/Solution-AI-Sprint7/Task1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A5EB33-A9F5-4540-9A2F-49945FCD7C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AFAE590-F6A5-9B44-8FC7-1F01DCA9F001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4160" yWindow="2680" windowWidth="28240" windowHeight="17240" xr2:uid="{D60D4A63-72E7-4F4F-A707-7ECDF5E29F8D}"/>
+    <workbookView xWindow="41280" yWindow="3980" windowWidth="28240" windowHeight="17240" xr2:uid="{D60D4A63-72E7-4F4F-A707-7ECDF5E29F8D}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="62">
   <si>
     <t>Инициатива</t>
   </si>
@@ -104,12 +104,6 @@
     <t>№</t>
   </si>
   <si>
-    <t>Недостаточно информации</t>
-  </si>
-  <si>
-    <t>Нужны критерии под выявлении подозрительных операций, не очень понятно какое дробление платежей и под какие пороги будет являться подозрительной операцией</t>
-  </si>
-  <si>
     <t>ML-кандидат</t>
   </si>
   <si>
@@ -194,9 +188,6 @@
     <t>Выход модели против бизнес выхода</t>
   </si>
   <si>
-    <t xml:space="preserve">Выявленая подозрительная операция (либо по определенному алгоритму, либо с помощью ML - зависит от ответов от бизнеса) </t>
-  </si>
-  <si>
     <t>2. Распознавать и оцифровывать сканы документов, приложенных к кредитной заявке.</t>
   </si>
   <si>
@@ -225,6 +216,12 @@
   </si>
   <si>
     <t>На выходе помечаются в автоматическом режиме операции с признаком подозрительные - для приоритизации разбора таких операций сотрудниками</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Выявленая подозрительная операция (с помощью ML ) </t>
+  </si>
+  <si>
+    <t>Нужны критерии под выявлении подозрительных операций, с помощью ML можно научить модель определять и помечать подозртиельные операции и выделять приоритет</t>
   </si>
 </sst>
 </file>
@@ -660,11 +657,11 @@
       <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="34" x14ac:dyDescent="0.2">
@@ -675,10 +672,10 @@
         <v>4</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -689,10 +686,10 @@
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="34" x14ac:dyDescent="0.2">
@@ -703,10 +700,10 @@
         <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -717,10 +714,10 @@
         <v>7</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="34" x14ac:dyDescent="0.2">
@@ -731,10 +728,10 @@
         <v>8</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -745,10 +742,10 @@
         <v>9</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="34" x14ac:dyDescent="0.2">
@@ -759,10 +756,10 @@
         <v>10</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -773,10 +770,10 @@
         <v>11</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="34" x14ac:dyDescent="0.2">
@@ -787,10 +784,10 @@
         <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="51" x14ac:dyDescent="0.2">
@@ -801,10 +798,10 @@
         <v>13</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -815,10 +812,10 @@
         <v>14</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="51" x14ac:dyDescent="0.2">
@@ -829,10 +826,10 @@
         <v>15</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -843,10 +840,10 @@
         <v>16</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -857,10 +854,10 @@
         <v>17</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -871,10 +868,10 @@
         <v>18</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -885,10 +882,10 @@
         <v>19</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="68" x14ac:dyDescent="0.2">
@@ -899,15 +896,15 @@
         <v>20</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -918,55 +915,55 @@
         <v>0</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="D23" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="D26" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
